--- a/KatalonData/EmailTextToPay/ManualEntry_CAN_Amount.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CAN_Amount.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E82D862-91DE-4F95-9BE4-7C70C1E91C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6944D44-E210-4BAB-9353-257F5A23010A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="ManualEntry_CAN_Amount" sheetId="1" r:id="rId1"/>
@@ -159,9 +159,6 @@
     <t>xyz</t>
   </si>
   <si>
-    <t>SC</t>
-  </si>
-  <si>
     <t>aaa</t>
   </si>
   <si>
@@ -198,31 +195,34 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Thu Feb 05 18:17:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 21:00:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 21:01:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 21:01:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 21:10:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Feb 06 19:50:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Feb 06 19:56:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Feb 06 19:58:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Feb 06 20:00:13 IST 2026</t>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 16:21:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 16:24:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 16:27:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 16:27:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 19:38:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 19:42:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 19:43:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 19:43:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 19:49:09 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -826,7 +826,7 @@
     </row>
     <row r="2" spans="1:27" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
@@ -844,7 +844,7 @@
         <v>44489405</v>
       </c>
       <c r="G2" s="6">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>38</v>
@@ -861,10 +861,10 @@
     </row>
     <row r="3" spans="1:27" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>37</v>
@@ -876,7 +876,7 @@
         <v>6</v>
       </c>
       <c r="F3" s="6">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="G3" s="6">
         <v>446.76</v>
@@ -896,13 +896,13 @@
     </row>
     <row r="4" spans="1:27" ht="62.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>4</v>
@@ -914,7 +914,7 @@
         <v>44489405</v>
       </c>
       <c r="G4" s="6">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>38</v>
@@ -934,13 +934,13 @@
     </row>
     <row r="5" spans="1:27" ht="62.5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
@@ -949,7 +949,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="6">
-        <v>98765431</v>
+        <v>1232</v>
       </c>
       <c r="G5" s="6">
         <v>446.76</v>
@@ -1001,7 +1001,9 @@
     <col min="12" max="12" width="16" style="6" customWidth="1" collapsed="1"/>
     <col min="13" max="13" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
     <col min="14" max="14" width="13.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="15" max="21" width="8.7265625" style="6" collapsed="1"/>
+    <col min="15" max="16" width="8.7265625" style="6" collapsed="1"/>
+    <col min="17" max="17" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="18" max="21" width="8.7265625" style="6" collapsed="1"/>
     <col min="22" max="22" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
     <col min="23" max="23" width="6.26953125" style="6" customWidth="1" collapsed="1"/>
     <col min="24" max="24" width="6" style="6" customWidth="1" collapsed="1"/>
@@ -1101,7 +1103,7 @@
     </row>
     <row r="2" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
@@ -1122,10 +1124,10 @@
         <v>446.76</v>
       </c>
       <c r="H2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>29</v>
@@ -1139,10 +1141,10 @@
     </row>
     <row r="3" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>34</v>
@@ -1160,10 +1162,10 @@
         <v>446.76</v>
       </c>
       <c r="H3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>29</v>
@@ -1175,28 +1177,28 @@
         <v>39</v>
       </c>
       <c r="M3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="P3" s="6">
         <v>123456</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="R3" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="T3" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="AB3" s="8" t="s">
         <v>33</v>
@@ -1204,10 +1206,10 @@
     </row>
     <row r="4" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>35</v>
@@ -1225,10 +1227,10 @@
         <v>446.76</v>
       </c>
       <c r="H4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>29</v>
@@ -1239,10 +1241,10 @@
     </row>
     <row r="5" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>36</v>
@@ -1260,10 +1262,10 @@
         <v>446.76</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="6">
@@ -1275,13 +1277,13 @@
     </row>
     <row r="6" spans="1:28" ht="50" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>4</v>
@@ -1296,10 +1298,10 @@
         <v>446.76</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>29</v>

--- a/KatalonData/EmailTextToPay/ManualEntry_CAN_Amount.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CAN_Amount.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6944D44-E210-4BAB-9353-257F5A23010A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246A12CE-0435-492D-A5BB-5B6A69719D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="ManualEntry_CAN_Amount" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="63">
   <si>
     <t>Result</t>
   </si>
@@ -198,31 +198,34 @@
     <t>South Carolina</t>
   </si>
   <si>
-    <t>Tue Feb 17 16:21:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 16:24:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 16:27:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 16:27:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 19:38:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 19:42:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 19:43:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 19:43:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 19:49:09 IST 2026</t>
+    <t>Mon Feb 23 17:58:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 18:00:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 18:01:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 18:03:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 18:05:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 18:09:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 18:12:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 18:13:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 18:15:18 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -844,7 +847,7 @@
         <v>44489405</v>
       </c>
       <c r="G2" s="6">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>38</v>
@@ -876,7 +879,7 @@
         <v>6</v>
       </c>
       <c r="F3" s="6">
-        <v>1231</v>
+        <v>1235</v>
       </c>
       <c r="G3" s="6">
         <v>446.76</v>
@@ -914,7 +917,7 @@
         <v>44489405</v>
       </c>
       <c r="G4" s="6">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>38</v>
@@ -949,7 +952,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="6">
-        <v>1232</v>
+        <v>1236</v>
       </c>
       <c r="G5" s="6">
         <v>446.76</v>
@@ -1103,10 +1106,10 @@
     </row>
     <row r="2" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>31</v>
@@ -1144,7 +1147,7 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>34</v>
@@ -1209,7 +1212,7 @@
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>35</v>
@@ -1244,7 +1247,7 @@
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>36</v>
@@ -1280,7 +1283,7 @@
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>50</v>

--- a/KatalonData/EmailTextToPay/ManualEntry_CAN_Amount.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CAN_Amount.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246A12CE-0435-492D-A5BB-5B6A69719D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{4D0EA9F6-0E28-414B-9516-6B5F24198B6E}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView activeTab="1" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
   <sheets>
-    <sheet name="ManualEntry_CAN_Amount" sheetId="1" r:id="rId1"/>
-    <sheet name="ManualEntry_CAN_Amount_Error" sheetId="2" r:id="rId2"/>
+    <sheet name="ManualEntry_CAN_Amount" r:id="rId1" sheetId="1"/>
+    <sheet name="ManualEntry_CAN_Amount_Error" r:id="rId2" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="77">
   <si>
     <t>Result</t>
   </si>
@@ -198,40 +198,83 @@
     <t>South Carolina</t>
   </si>
   <si>
-    <t>Mon Feb 23 17:58:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 18:00:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 18:01:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 18:03:32 IST 2026</t>
+    <t>Thu Mar 19 22:46:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:47:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:47:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:48:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:54:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:55:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:55:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:56:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:57:02 IST 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:10:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:11:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:11:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:12:33 IST 2026</t>
   </si>
   <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>Mon Feb 23 18:05:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 18:09:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 18:12:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 18:13:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 18:15:18 IST 2026</t>
+    <t>Wed Mar 25 18:13:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:14:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:14:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:15:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:15:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:16:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:17:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:17:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:18:21 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -333,66 +376,66 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="4" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="5" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="5" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="2" fontId="3" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="3" fontId="3" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="3" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="3" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="8" name="Hyperlink" xfId="1"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -409,10 +452,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -447,7 +490,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -499,7 +542,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -610,21 +653,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -641,7 +684,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -713,38 +756,38 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:AA5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+  <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.7265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="16.6328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="25" style="4" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8.7265625" style="1" collapsed="1"/>
-    <col min="5" max="5" width="15" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="12.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="8.1796875" style="6" customWidth="1" collapsed="1"/>
-    <col min="8" max="9" width="10.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="17.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="16" style="6" customWidth="1" collapsed="1"/>
-    <col min="13" max="14" width="14.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="9.1796875" style="6" customWidth="1" collapsed="1"/>
-    <col min="17" max="17" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="8.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="19" max="27" width="8.7265625" style="6" collapsed="1"/>
-    <col min="28" max="16384" width="8.7265625" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="6.7265625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="16.6328125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="4" width="25.0" collapsed="true"/>
+    <col min="4" max="4" style="1" width="8.7265625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="15.0" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="6" width="12.54296875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="6" width="8.1796875" collapsed="true"/>
+    <col min="8" max="9" customWidth="true" style="6" width="10.36328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="6" width="17.7265625" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="6" width="16.0" collapsed="true"/>
+    <col min="13" max="14" customWidth="true" style="6" width="14.453125" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
+    <col min="16" max="16" customWidth="true" style="6" width="9.1796875" collapsed="true"/>
+    <col min="17" max="17" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
+    <col min="18" max="18" customWidth="true" style="6" width="8.54296875" collapsed="true"/>
+    <col min="19" max="27" style="6" width="8.7265625" collapsed="true"/>
+    <col min="28" max="16384" style="1" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row customFormat="1" r="1" s="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -827,12 +870,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>32</v>
@@ -862,12 +905,12 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>37</v>
@@ -897,12 +940,12 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="62.5" x14ac:dyDescent="0.25">
+    <row ht="62.5" r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>48</v>
@@ -935,12 +978,12 @@
         <v>22201</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="62.5" x14ac:dyDescent="0.25">
+    <row ht="62.5" r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>49</v>
@@ -976,46 +1019,46 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J3" r:id="rId1" xr:uid="{FE47C787-DE99-4492-A8B2-4EBE54ABB261}"/>
-    <hyperlink ref="J2" r:id="rId2" xr:uid="{D2C11198-27F8-408D-8A6B-64C9B9DF0F92}"/>
-    <hyperlink ref="J5" r:id="rId3" xr:uid="{6A159962-5D60-427C-9730-B7B753DCF218}"/>
-    <hyperlink ref="J4" r:id="rId4" xr:uid="{064B7228-C8DF-4F7F-9129-CEED06BA7374}"/>
+    <hyperlink r:id="rId1" ref="J3" xr:uid="{FE47C787-DE99-4492-A8B2-4EBE54ABB261}"/>
+    <hyperlink r:id="rId2" ref="J2" xr:uid="{D2C11198-27F8-408D-8A6B-64C9B9DF0F92}"/>
+    <hyperlink r:id="rId3" ref="J5" xr:uid="{6A159962-5D60-427C-9730-B7B753DCF218}"/>
+    <hyperlink r:id="rId4" ref="J4" xr:uid="{064B7228-C8DF-4F7F-9129-CEED06BA7374}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:AB6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="15.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="36" style="8" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8.7265625" style="6" collapsed="1"/>
-    <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="11.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="10.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="10.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="16.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="12" style="6" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="16" style="6" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="13.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="8.7265625" style="6" collapsed="1"/>
-    <col min="17" max="17" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="21" width="8.7265625" style="6" collapsed="1"/>
-    <col min="22" max="22" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="6.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="6" style="6" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="5.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="6.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="47.08984375" style="8" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="24.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="30" max="16384" width="8.7265625" style="6" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="6" width="15.90625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="8" width="36.0" collapsed="true"/>
+    <col min="4" max="4" style="6" width="8.7265625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="6" width="18.453125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="6" width="9.36328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="6" width="11.36328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="6" width="10.7265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="6" width="10.54296875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="6" width="16.453125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="6" width="12.0" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="6" width="16.0" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
+    <col min="14" max="14" customWidth="true" style="6" width="13.453125" collapsed="true"/>
+    <col min="15" max="16" style="6" width="8.7265625" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
+    <col min="18" max="21" style="6" width="8.7265625" collapsed="true"/>
+    <col min="22" max="22" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" style="6" width="6.26953125" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="6" width="6.0" collapsed="true"/>
+    <col min="25" max="25" customWidth="true" style="6" width="5.90625" collapsed="true"/>
+    <col min="26" max="26" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
+    <col min="27" max="27" customWidth="true" style="6" width="6.54296875" collapsed="true"/>
+    <col min="28" max="28" customWidth="true" style="8" width="47.08984375" collapsed="true"/>
+    <col min="29" max="29" customWidth="true" style="6" width="24.81640625" collapsed="true"/>
+    <col min="30" max="16384" style="6" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -1104,12 +1147,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>31</v>
@@ -1142,12 +1185,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>34</v>
@@ -1207,12 +1250,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>35</v>
@@ -1242,12 +1285,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row customHeight="1" ht="42" r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>36</v>
@@ -1278,12 +1321,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="50" x14ac:dyDescent="0.25">
+    <row ht="50" r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>50</v>
@@ -1324,12 +1367,12 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" xr:uid="{116CABED-82C4-49A6-B1D3-FB007D34A91E}"/>
-    <hyperlink ref="J3" r:id="rId2" xr:uid="{8C433AE8-EA1A-4C8E-A7C0-0BB281ABB9A1}"/>
-    <hyperlink ref="J4" r:id="rId3" xr:uid="{A312AB03-1536-49D3-9B02-6827CCAB91D2}"/>
-    <hyperlink ref="J6" r:id="rId4" xr:uid="{FDC2FBF7-47EE-439C-A052-EF8B1027F8CA}"/>
+    <hyperlink r:id="rId1" ref="J2" xr:uid="{116CABED-82C4-49A6-B1D3-FB007D34A91E}"/>
+    <hyperlink r:id="rId2" ref="J3" xr:uid="{8C433AE8-EA1A-4C8E-A7C0-0BB281ABB9A1}"/>
+    <hyperlink r:id="rId3" ref="J4" xr:uid="{A312AB03-1536-49D3-9B02-6827CCAB91D2}"/>
+    <hyperlink r:id="rId4" ref="J6" xr:uid="{FDC2FBF7-47EE-439C-A052-EF8B1027F8CA}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/ManualEntry_CAN_Amount.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CAN_Amount.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="81">
   <si>
     <t>Result</t>
   </si>
@@ -268,6 +268,18 @@
   </si>
   <si>
     <t>Wed Mar 25 18:18:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:40:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:41:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:41:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:42:37 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -875,7 +887,7 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>32</v>
@@ -910,7 +922,7 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>37</v>
@@ -945,7 +957,7 @@
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>48</v>
@@ -983,7 +995,7 @@
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>49</v>

--- a/KatalonData/EmailTextToPay/ManualEntry_CAN_Amount.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CAN_Amount.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="95">
   <si>
     <t>Result</t>
   </si>
@@ -280,6 +280,48 @@
   </si>
   <si>
     <t>Thu Apr 23 15:42:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:46:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:47:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:47:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:48:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:49:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:49:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:50:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:51:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:52:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:52:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:53:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:54:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:55:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:56:14 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -887,7 +929,7 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>32</v>
@@ -922,7 +964,7 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>37</v>
@@ -957,7 +999,7 @@
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>48</v>
@@ -995,7 +1037,7 @@
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>49</v>
@@ -1164,7 +1206,7 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>31</v>
@@ -1202,7 +1244,7 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>34</v>
@@ -1267,7 +1309,7 @@
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>35</v>
@@ -1302,7 +1344,7 @@
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>36</v>
@@ -1338,7 +1380,7 @@
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>50</v>

--- a/KatalonData/EmailTextToPay/ManualEntry_CAN_Amount.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CAN_Amount.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{4D0EA9F6-0E28-414B-9516-6B5F24198B6E}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA845D22-0926-45FB-A903-358DE0F249C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="1" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
-    <sheet name="ManualEntry_CAN_Amount" r:id="rId1" sheetId="1"/>
-    <sheet name="ManualEntry_CAN_Amount_Error" r:id="rId2" sheetId="2"/>
+    <sheet name="ManualEntry_CAN_Amount" sheetId="1" r:id="rId1"/>
+    <sheet name="ManualEntry_CAN_Amount_Error" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="63">
   <si>
     <t>Result</t>
   </si>
@@ -138,9 +138,6 @@
     <t>Payment app+mandatory values+already used CAN+new Amount</t>
   </si>
   <si>
-    <t>An Active Payment Link Already Exists with the Same Client Account Number and Amount</t>
-  </si>
-  <si>
     <t>Payment app+mandatory+non mandatory values+already used CAN+already used Amount</t>
   </si>
   <si>
@@ -198,123 +195,12 @@
     <t>South Carolina</t>
   </si>
   <si>
-    <t>Thu Mar 19 22:46:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:47:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:47:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:48:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:54:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:55:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:55:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:56:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:57:02 IST 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:10:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:11:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:11:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:12:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:13:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:14:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:14:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:15:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:15:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:16:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:17:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:17:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:18:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 15:40:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 15:41:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 15:41:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 15:42:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:46:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:47:04 IST 2026</t>
-  </si>
-  <si>
     <t>Thu Apr 30 14:47:46 IST 2026</t>
   </si>
   <si>
     <t>Thu Apr 30 14:48:28 IST 2026</t>
   </si>
   <si>
-    <t>Thu Apr 30 14:49:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:49:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:50:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:51:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:52:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:52:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:53:38 IST 2026</t>
-  </si>
-  <si>
     <t>Thu Apr 30 14:54:32 IST 2026</t>
   </si>
   <si>
@@ -322,13 +208,30 @@
   </si>
   <si>
     <t>Thu Apr 30 14:56:14 IST 2026</t>
+  </si>
+  <si>
+    <t>DueDate</t>
+  </si>
+  <si>
+    <t>Mon May 11 15:28:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 15:29:07 IST 2026</t>
+  </si>
+  <si>
+    <t>An Active Payment Link Already Exists with the Same Client Account Number and Amount.</t>
+  </si>
+  <si>
+    <t>Mon May 11 15:37:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 15:38:11 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -430,66 +333,69 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="4" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="5" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="5" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="2" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="3" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle builtinId="8" name="Hyperlink" xfId="1"/>
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -506,10 +412,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -544,7 +450,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -596,7 +502,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -707,21 +613,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -738,7 +644,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -810,38 +716,39 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
   <dimension ref="A1:AB5"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="6.7265625" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="16.6328125" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="4" width="25.0" collapsed="true"/>
-    <col min="4" max="4" style="1" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="15.0" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="6" width="12.54296875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="6" width="8.1796875" collapsed="true"/>
-    <col min="8" max="9" customWidth="true" style="6" width="10.36328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="6" width="17.7265625" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="6" width="16.0" collapsed="true"/>
-    <col min="13" max="14" customWidth="true" style="6" width="14.453125" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
-    <col min="16" max="16" customWidth="true" style="6" width="9.1796875" collapsed="true"/>
-    <col min="17" max="17" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
-    <col min="18" max="18" customWidth="true" style="6" width="8.54296875" collapsed="true"/>
-    <col min="19" max="27" style="6" width="8.7265625" collapsed="true"/>
-    <col min="28" max="16384" style="1" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.7265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="16.6328125" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="25" style="4" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.7265625" style="1" collapsed="1"/>
+    <col min="5" max="5" width="15" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="12.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="8.1796875" style="6" customWidth="1" collapsed="1"/>
+    <col min="8" max="9" width="10.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="17.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="16" style="6" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="10.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="14" max="15" width="14.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="16" max="16" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="17" max="17" width="9.1796875" style="6" customWidth="1" collapsed="1"/>
+    <col min="18" max="18" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="19" max="19" width="8.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="20" max="28" width="8.7265625" style="6" collapsed="1"/>
+    <col min="29" max="16384" width="8.7265625" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" r="1" s="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -879,57 +786,60 @@
         <v>21</v>
       </c>
       <c r="M1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="R1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="U1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="V1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="W1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="X1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="Y1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Z1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="AA1" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="AB1" s="10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row ht="37.5" r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>32</v>
@@ -944,13 +854,13 @@
         <v>44489405</v>
       </c>
       <c r="G2" s="6">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>29</v>
@@ -958,16 +868,19 @@
       <c r="K2" s="6">
         <v>1234567890</v>
       </c>
+      <c r="M2" s="17" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row ht="37.5" r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>4</v>
@@ -976,16 +889,16 @@
         <v>6</v>
       </c>
       <c r="F3" s="6">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="G3" s="6">
         <v>446.76</v>
       </c>
       <c r="H3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>29</v>
@@ -994,15 +907,15 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row ht="62.5" r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="62.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>4</v>
@@ -1017,10 +930,10 @@
         <v>107</v>
       </c>
       <c r="H4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>29</v>
@@ -1028,19 +941,19 @@
       <c r="K4" s="6">
         <v>1234567890</v>
       </c>
-      <c r="P4" s="6">
+      <c r="Q4" s="6">
         <v>22201</v>
       </c>
     </row>
-    <row ht="62.5" r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="62.5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
@@ -1055,10 +968,10 @@
         <v>446.76</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>29</v>
@@ -1066,56 +979,57 @@
       <c r="K5" s="6">
         <v>1234567890</v>
       </c>
-      <c r="P5" s="6">
+      <c r="Q5" s="6">
         <v>22201</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="J3" xr:uid="{FE47C787-DE99-4492-A8B2-4EBE54ABB261}"/>
-    <hyperlink r:id="rId2" ref="J2" xr:uid="{D2C11198-27F8-408D-8A6B-64C9B9DF0F92}"/>
-    <hyperlink r:id="rId3" ref="J5" xr:uid="{6A159962-5D60-427C-9730-B7B753DCF218}"/>
-    <hyperlink r:id="rId4" ref="J4" xr:uid="{064B7228-C8DF-4F7F-9129-CEED06BA7374}"/>
+    <hyperlink ref="J3" r:id="rId1" xr:uid="{FE47C787-DE99-4492-A8B2-4EBE54ABB261}"/>
+    <hyperlink ref="J2" r:id="rId2" xr:uid="{D2C11198-27F8-408D-8A6B-64C9B9DF0F92}"/>
+    <hyperlink ref="J5" r:id="rId3" xr:uid="{6A159962-5D60-427C-9730-B7B753DCF218}"/>
+    <hyperlink ref="J4" r:id="rId4" xr:uid="{064B7228-C8DF-4F7F-9129-CEED06BA7374}"/>
   </hyperlinks>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
   <dimension ref="A1:AC6"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="6" width="15.90625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="8" width="36.0" collapsed="true"/>
-    <col min="4" max="4" style="6" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="6" width="18.453125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="6" width="9.36328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="6" width="11.36328125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="6" width="10.7265625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="6" width="10.54296875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="6" width="16.453125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="6" width="12.0" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="6" width="16.0" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="6" width="13.453125" collapsed="true"/>
-    <col min="15" max="16" style="6" width="8.7265625" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
-    <col min="18" max="21" style="6" width="8.7265625" collapsed="true"/>
-    <col min="22" max="22" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
-    <col min="23" max="23" customWidth="true" style="6" width="6.26953125" collapsed="true"/>
-    <col min="24" max="24" customWidth="true" style="6" width="6.0" collapsed="true"/>
-    <col min="25" max="25" customWidth="true" style="6" width="5.90625" collapsed="true"/>
-    <col min="26" max="26" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
-    <col min="27" max="27" customWidth="true" style="6" width="6.54296875" collapsed="true"/>
-    <col min="28" max="28" customWidth="true" style="8" width="47.08984375" collapsed="true"/>
-    <col min="29" max="29" customWidth="true" style="6" width="24.81640625" collapsed="true"/>
-    <col min="30" max="16384" style="6" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="15.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="36" style="8" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.7265625" style="6" collapsed="1"/>
+    <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="11.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="10.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="10.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="16.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="12" style="6" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="16" style="6" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="10.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="13.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="16" max="17" width="8.7265625" style="6" collapsed="1"/>
+    <col min="18" max="18" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="19" max="22" width="8.7265625" style="6" collapsed="1"/>
+    <col min="23" max="23" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="6.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="6" style="6" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="5.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="28" max="28" width="6.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="29" max="29" width="47.08984375" style="8" customWidth="1" collapsed="1"/>
+    <col min="30" max="30" width="24.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="31" max="16384" width="8.7265625" style="6" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1153,60 +1067,63 @@
         <v>21</v>
       </c>
       <c r="M1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="R1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="U1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="V1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="W1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="11" t="s">
+      <c r="X1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="Y1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="11" t="s">
+      <c r="Z1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="11" t="s">
+      <c r="AA1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" s="11" t="s">
+      <c r="AB1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="AC1" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row ht="37.5" r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>31</v>
@@ -1224,10 +1141,10 @@
         <v>446.76</v>
       </c>
       <c r="H2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>29</v>
@@ -1235,19 +1152,22 @@
       <c r="K2" s="6">
         <v>1234567890</v>
       </c>
-      <c r="AB2" s="8" t="s">
+      <c r="M2" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC2" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row ht="37.5" r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>4</v>
@@ -1262,10 +1182,10 @@
         <v>446.76</v>
       </c>
       <c r="H3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>29</v>
@@ -1274,45 +1194,45 @@
         <v>1234567890</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="Q3" s="6">
+        <v>123456</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="S3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="P3" s="6">
-        <v>123456</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="R3" s="6" t="s">
+      <c r="T3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="U3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="T3" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB3" s="8" t="s">
-        <v>33</v>
+      <c r="AC3" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row ht="37.5" r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>4</v>
@@ -1327,27 +1247,27 @@
         <v>446.76</v>
       </c>
       <c r="H4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="AB4" s="8" t="s">
-        <v>33</v>
+      <c r="AC4" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row customHeight="1" ht="42" r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>4</v>
@@ -1362,28 +1282,28 @@
         <v>446.76</v>
       </c>
       <c r="H5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="6">
         <v>1234567890</v>
       </c>
-      <c r="AB5" s="8" t="s">
-        <v>33</v>
+      <c r="AC5" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row ht="50" r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="50" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>4</v>
@@ -1398,10 +1318,10 @@
         <v>446.76</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>29</v>
@@ -1410,23 +1330,23 @@
         <v>1234567890</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="P6" s="6">
+        <v>38</v>
+      </c>
+      <c r="Q6" s="6">
         <v>22201</v>
       </c>
-      <c r="AB6" s="8" t="s">
-        <v>33</v>
+      <c r="AC6" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="J2" xr:uid="{116CABED-82C4-49A6-B1D3-FB007D34A91E}"/>
-    <hyperlink r:id="rId2" ref="J3" xr:uid="{8C433AE8-EA1A-4C8E-A7C0-0BB281ABB9A1}"/>
-    <hyperlink r:id="rId3" ref="J4" xr:uid="{A312AB03-1536-49D3-9B02-6827CCAB91D2}"/>
-    <hyperlink r:id="rId4" ref="J6" xr:uid="{FDC2FBF7-47EE-439C-A052-EF8B1027F8CA}"/>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{116CABED-82C4-49A6-B1D3-FB007D34A91E}"/>
+    <hyperlink ref="J3" r:id="rId2" xr:uid="{8C433AE8-EA1A-4C8E-A7C0-0BB281ABB9A1}"/>
+    <hyperlink ref="J4" r:id="rId3" xr:uid="{A312AB03-1536-49D3-9B02-6827CCAB91D2}"/>
+    <hyperlink ref="J6" r:id="rId4" xr:uid="{FDC2FBF7-47EE-439C-A052-EF8B1027F8CA}"/>
   </hyperlinks>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>